--- a/ig/improve-doc/CodeSystem-terminologie-cim11-mms.xlsx
+++ b/ig/improve-doc/CodeSystem-terminologie-cim11-mms.xlsx
@@ -67,7 +67,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-27T13:33:30+00:00</t>
+    <t>2024-11-06T15:55:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/improve-doc/CodeSystem-terminologie-cim11-mms.xlsx
+++ b/ig/improve-doc/CodeSystem-terminologie-cim11-mms.xlsx
@@ -31,7 +31,7 @@
     <t>Identifier</t>
   </si>
   <si>
-    <t>https://smt.esante.gouv.fr/#terminologie-cim11-mms</t>
+    <t>OID:2.16.840.1.113883.6.347</t>
   </si>
   <si>
     <t>Version</t>
@@ -49,7 +49,7 @@
     <t>Title</t>
   </si>
   <si>
-    <t>Classification Internationale des Maladies 11ème révision pour les statistiques de mortalité et de morbidité</t>
+    <t>Classification internationale des maladies (11eme révision). Linéarisation pour les statistiques de morbi-mortalité</t>
   </si>
   <si>
     <t>Status</t>
@@ -67,7 +67,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-06T15:55:45+00:00</t>
+    <t>2024-11-26T12:51:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/improve-doc/CodeSystem-terminologie-cim11-mms.xlsx
+++ b/ig/improve-doc/CodeSystem-terminologie-cim11-mms.xlsx
@@ -67,7 +67,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-26T12:51:17+00:00</t>
+    <t>2024-11-26T14:12:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/improve-doc/CodeSystem-terminologie-cim11-mms.xlsx
+++ b/ig/improve-doc/CodeSystem-terminologie-cim11-mms.xlsx
@@ -67,7 +67,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-26T14:12:54+00:00</t>
+    <t>2024-12-02T10:46:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/improve-doc/CodeSystem-terminologie-cim11-mms.xlsx
+++ b/ig/improve-doc/CodeSystem-terminologie-cim11-mms.xlsx
@@ -67,7 +67,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-02T10:46:43+00:00</t>
+    <t>2024-12-02T16:50:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/improve-doc/CodeSystem-terminologie-cim11-mms.xlsx
+++ b/ig/improve-doc/CodeSystem-terminologie-cim11-mms.xlsx
@@ -67,7 +67,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-02T16:50:25+00:00</t>
+    <t>2024-12-04T07:44:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
